--- a/erp-server/erp-server-tms/src/main/resources/excel/shippingCalculation.xlsx
+++ b/erp-server/erp-server-tms/src/main/resources/excel/shippingCalculation.xlsx
@@ -1025,8 +1025,7 @@
     <col min="5" max="5" width="21.5" customWidth="1"/>
     <col min="6" max="6" width="13.75" customWidth="1"/>
     <col min="7" max="7" width="17.375" customWidth="1"/>
-    <col min="8" max="8" width="12.75" customWidth="1"/>
-    <col min="9" max="9" width="17.125" customWidth="1"/>
+    <col min="8" max="9" width="20.5" customWidth="1"/>
     <col min="10" max="10" width="29.75" customWidth="1"/>
     <col min="11" max="11" width="14.125" customWidth="1"/>
   </cols>
